--- a/backend/data/financials_by_company/1293.HK.xlsx
+++ b/backend/data/financials_by_company/1293.HK.xlsx
@@ -662,144 +662,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-35337250</v>
+        <v>-1539500</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1229370000</v>
+        <v>2049784000</v>
       </c>
       <c r="E2" t="n">
-        <v>55187000</v>
+        <v>-6158000</v>
       </c>
       <c r="F2" t="n">
-        <v>-141349000</v>
+        <v>-6158000</v>
       </c>
       <c r="G2" t="n">
-        <v>125747000</v>
+        <v>551986000</v>
       </c>
       <c r="H2" t="n">
-        <v>523001000</v>
+        <v>536533000</v>
       </c>
       <c r="I2" t="n">
-        <v>30612366000</v>
+        <v>35296852000</v>
       </c>
       <c r="J2" t="n">
-        <v>1284557000</v>
+        <v>2043626000</v>
       </c>
       <c r="K2" t="n">
-        <v>761556000</v>
+        <v>1507093000</v>
       </c>
       <c r="L2" t="n">
-        <v>-541341000</v>
+        <v>-575728000</v>
       </c>
       <c r="M2" t="n">
-        <v>532455000</v>
+        <v>598008000</v>
       </c>
       <c r="N2" t="n">
-        <v>9325000</v>
+        <v>22280000</v>
       </c>
       <c r="O2" t="n">
-        <v>428294750</v>
+        <v>556604500</v>
       </c>
       <c r="P2" t="n">
-        <v>125747000</v>
+        <v>551986000</v>
       </c>
       <c r="Q2" t="n">
-        <v>32264652000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>39671000</v>
-      </c>
+        <v>37126430000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>787681000</v>
+        <v>1478976000</v>
       </c>
       <c r="T2" t="n">
         <v>2837511429</v>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>2837511429</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.19</v>
+      </c>
       <c r="W2" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="X2" t="n">
-        <v>125747000</v>
+        <v>551986000</v>
       </c>
       <c r="Y2" t="n">
-        <v>125747000</v>
+        <v>551986000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>125747000</v>
+        <v>551986000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11654000</v>
+        <v>8627000</v>
       </c>
       <c r="AC2" t="n">
-        <v>114093000</v>
+        <v>543359000</v>
       </c>
       <c r="AD2" t="n">
-        <v>114093000</v>
+        <v>543359000</v>
       </c>
       <c r="AE2" t="n">
-        <v>115008000</v>
+        <v>365726000</v>
       </c>
       <c r="AF2" t="n">
-        <v>229101000</v>
+        <v>909085000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1265604000</v>
+        <v>1071154000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-186562000</v>
+        <v>-6158000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-9974000</v>
+        <v>6158000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-541341000</v>
+        <v>-575728000</v>
       </c>
       <c r="AK2" t="n">
-        <v>18211000</v>
+        <v>19793000</v>
       </c>
       <c r="AL2" t="n">
-        <v>532455000</v>
+        <v>598008000</v>
       </c>
       <c r="AM2" t="n">
-        <v>9325000</v>
+        <v>22280000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-357673000</v>
+        <v>456214000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1652286000</v>
+        <v>1829578000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1730025000</v>
+        <v>1917665000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1099982000</v>
+        <v>1211204000</v>
       </c>
       <c r="AR2" t="n">
-        <v>630043000</v>
+        <v>706461000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1294613000</v>
+        <v>2285792000</v>
       </c>
       <c r="AT2" t="n">
-        <v>30612366000</v>
+        <v>35296852000</v>
       </c>
       <c r="AU2" t="n">
-        <v>31906979000</v>
+        <v>37582644000</v>
       </c>
       <c r="AV2" t="n">
-        <v>31906979000</v>
+        <v>37582644000</v>
       </c>
     </row>
     <row r="3">
@@ -950,146 +952,144 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1539500</v>
+        <v>-35337250</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>2049784000</v>
+        <v>1229370000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6158000</v>
+        <v>55187000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6158000</v>
+        <v>-141349000</v>
       </c>
       <c r="G4" t="n">
-        <v>551986000</v>
+        <v>125747000</v>
       </c>
       <c r="H4" t="n">
-        <v>536533000</v>
+        <v>523001000</v>
       </c>
       <c r="I4" t="n">
-        <v>35296852000</v>
+        <v>30612366000</v>
       </c>
       <c r="J4" t="n">
-        <v>2043626000</v>
+        <v>1284557000</v>
       </c>
       <c r="K4" t="n">
-        <v>1507093000</v>
+        <v>761556000</v>
       </c>
       <c r="L4" t="n">
-        <v>-575728000</v>
+        <v>-541341000</v>
       </c>
       <c r="M4" t="n">
-        <v>598008000</v>
+        <v>532455000</v>
       </c>
       <c r="N4" t="n">
-        <v>22280000</v>
+        <v>9325000</v>
       </c>
       <c r="O4" t="n">
-        <v>556604500</v>
+        <v>428294750</v>
       </c>
       <c r="P4" t="n">
-        <v>551986000</v>
+        <v>125747000</v>
       </c>
       <c r="Q4" t="n">
-        <v>37126430000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>32264652000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>39671000</v>
+      </c>
       <c r="S4" t="n">
-        <v>1478976000</v>
+        <v>787681000</v>
       </c>
       <c r="T4" t="n">
         <v>2837511429</v>
       </c>
-      <c r="U4" t="n">
-        <v>2837511429</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.19</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="X4" t="n">
-        <v>551986000</v>
+        <v>125747000</v>
       </c>
       <c r="Y4" t="n">
-        <v>551986000</v>
+        <v>125747000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>551986000</v>
+        <v>125747000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8627000</v>
+        <v>11654000</v>
       </c>
       <c r="AC4" t="n">
-        <v>543359000</v>
+        <v>114093000</v>
       </c>
       <c r="AD4" t="n">
-        <v>543359000</v>
+        <v>114093000</v>
       </c>
       <c r="AE4" t="n">
-        <v>365726000</v>
+        <v>115008000</v>
       </c>
       <c r="AF4" t="n">
-        <v>909085000</v>
+        <v>229101000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1071154000</v>
+        <v>1265604000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6158000</v>
+        <v>-186562000</v>
       </c>
       <c r="AI4" t="n">
-        <v>6158000</v>
+        <v>-9974000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-575728000</v>
+        <v>-541341000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19793000</v>
+        <v>18211000</v>
       </c>
       <c r="AL4" t="n">
-        <v>598008000</v>
+        <v>532455000</v>
       </c>
       <c r="AM4" t="n">
-        <v>22280000</v>
+        <v>9325000</v>
       </c>
       <c r="AN4" t="n">
-        <v>456214000</v>
+        <v>-357673000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1829578000</v>
+        <v>1652286000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1917665000</v>
+        <v>1730025000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1211204000</v>
+        <v>1099982000</v>
       </c>
       <c r="AR4" t="n">
-        <v>706461000</v>
+        <v>630043000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2285792000</v>
+        <v>1294613000</v>
       </c>
       <c r="AT4" t="n">
-        <v>35296852000</v>
+        <v>30612366000</v>
       </c>
       <c r="AU4" t="n">
-        <v>37582644000</v>
+        <v>31906979000</v>
       </c>
       <c r="AV4" t="n">
-        <v>37582644000</v>
+        <v>31906979000</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2837511429</v>
@@ -1479,46 +1479,44 @@
         <v>2837511429</v>
       </c>
       <c r="D2" t="n">
-        <v>9094165000</v>
+        <v>10995187000</v>
       </c>
       <c r="E2" t="n">
-        <v>10321610000</v>
+        <v>14003571000</v>
       </c>
       <c r="F2" t="n">
-        <v>5430031000</v>
+        <v>6111616000</v>
       </c>
       <c r="G2" t="n">
-        <v>17044864000</v>
+        <v>21384427000</v>
       </c>
       <c r="H2" t="n">
-        <v>3662570000</v>
+        <v>4945092000</v>
       </c>
       <c r="I2" t="n">
-        <v>5430031000</v>
+        <v>6111616000</v>
       </c>
       <c r="J2" t="n">
-        <v>1037734000</v>
+        <v>1305323000</v>
       </c>
       <c r="K2" t="n">
-        <v>7760988000</v>
+        <v>8686179000</v>
       </c>
       <c r="L2" t="n">
-        <v>8257706000</v>
+        <v>9215916000</v>
       </c>
       <c r="M2" t="n">
-        <v>7735301000</v>
+        <v>8674645000</v>
       </c>
       <c r="N2" t="n">
-        <v>-25687000</v>
+        <v>-11534000</v>
       </c>
       <c r="O2" t="n">
-        <v>7760988000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>107994000</v>
-      </c>
+        <v>8686179000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>4529034000</v>
+        <v>5183337000</v>
       </c>
       <c r="R2" t="n">
         <v>2372982000</v>
@@ -1530,155 +1528,161 @@
         <v>23277000</v>
       </c>
       <c r="U2" t="n">
-        <v>15357621000</v>
+        <v>19420022000</v>
       </c>
       <c r="V2" t="n">
-        <v>3916641000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>4982111000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>2044914000</v>
+        <v>2806224000</v>
       </c>
       <c r="Y2" t="n">
-        <v>428062000</v>
+        <v>467031000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1443665000</v>
+        <v>1708856000</v>
       </c>
       <c r="AA2" t="n">
-        <v>946947000</v>
+        <v>1179119000</v>
       </c>
       <c r="AB2" t="n">
-        <v>496718000</v>
+        <v>529737000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11440980000</v>
+        <v>14437911000</v>
       </c>
       <c r="AD2" t="n">
-        <v>8877945000</v>
+        <v>12294715000</v>
       </c>
       <c r="AE2" t="n">
-        <v>90787000</v>
+        <v>126204000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8787158000</v>
+        <v>12168511000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1932473000</v>
+        <v>1350523000</v>
       </c>
       <c r="AH2" t="n">
-        <v>676684000</v>
+        <v>221425000</v>
       </c>
       <c r="AI2" t="n">
-        <v>679577000</v>
+        <v>766979000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>576212000</v>
+        <v>362119000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23092922000</v>
+        <v>28094667000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7989372000</v>
+        <v>8711664000</v>
       </c>
       <c r="AM2" t="n">
-        <v>29958000</v>
+        <v>62734000</v>
       </c>
       <c r="AN2" t="n">
-        <v>352947000</v>
+        <v>225677000</v>
       </c>
       <c r="AO2" t="n">
-        <v>220704000</v>
+        <v>252685000</v>
       </c>
       <c r="AP2" t="n">
-        <v>97396000</v>
+        <v>102248000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>123308000</v>
+        <v>150437000</v>
       </c>
       <c r="AR2" t="n">
-        <v>358031000</v>
+        <v>394316000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2330957000</v>
+        <v>2574563000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1187541000</v>
+        <v>1352547000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1143416000</v>
+        <v>1222016000</v>
       </c>
       <c r="AV2" t="n">
-        <v>4607474000</v>
+        <v>5122080000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-2442997000</v>
+        <v>-2172453000</v>
       </c>
       <c r="AX2" t="n">
-        <v>7050471000</v>
+        <v>7294533000</v>
       </c>
       <c r="AY2" t="n">
-        <v>78745000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>48363000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5122080000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>1420195000</v>
+        <v>1359696000</v>
       </c>
       <c r="BB2" t="n">
-        <v>5082511000</v>
+        <v>5303314000</v>
       </c>
       <c r="BC2" t="n">
-        <v>469020000</v>
+        <v>583160000</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>15103550000</v>
+        <v>19383003000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1371384000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>3249125000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3541551000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>3577652000</v>
+        <v>2782521000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-46722000</v>
+        <v>-33508000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3236011000</v>
+        <v>2472712000</v>
       </c>
       <c r="BK2" t="n">
-        <v>388363000</v>
+        <v>343317000</v>
       </c>
       <c r="BL2" t="n">
-        <v>8945611000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>7461873000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>106991000</v>
+      </c>
       <c r="BN2" t="n">
-        <v>764120000</v>
+        <v>376991000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-16934000</v>
+        <v>-3644000</v>
       </c>
       <c r="BP2" t="n">
-        <v>781054000</v>
+        <v>380635000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>324280000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>134569000</v>
-      </c>
+        <v>1703061000</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>189711000</v>
+        <v>1703061000</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="BU2" t="n">
-        <v>189711000</v>
+        <v>1693061000</v>
       </c>
     </row>
     <row r="3">
@@ -1902,7 +1906,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2837511429</v>
@@ -1911,44 +1915,46 @@
         <v>2837511429</v>
       </c>
       <c r="D4" t="n">
-        <v>10995187000</v>
+        <v>9094165000</v>
       </c>
       <c r="E4" t="n">
-        <v>14003571000</v>
+        <v>10321610000</v>
       </c>
       <c r="F4" t="n">
-        <v>6111616000</v>
+        <v>5430031000</v>
       </c>
       <c r="G4" t="n">
-        <v>21384427000</v>
+        <v>17044864000</v>
       </c>
       <c r="H4" t="n">
-        <v>4945092000</v>
+        <v>3662570000</v>
       </c>
       <c r="I4" t="n">
-        <v>6111616000</v>
+        <v>5430031000</v>
       </c>
       <c r="J4" t="n">
-        <v>1305323000</v>
+        <v>1037734000</v>
       </c>
       <c r="K4" t="n">
-        <v>8686179000</v>
+        <v>7760988000</v>
       </c>
       <c r="L4" t="n">
-        <v>9215916000</v>
+        <v>8257706000</v>
       </c>
       <c r="M4" t="n">
-        <v>8674645000</v>
+        <v>7735301000</v>
       </c>
       <c r="N4" t="n">
-        <v>-11534000</v>
+        <v>-25687000</v>
       </c>
       <c r="O4" t="n">
-        <v>8686179000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>7760988000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>107994000</v>
+      </c>
       <c r="Q4" t="n">
-        <v>5183337000</v>
+        <v>4529034000</v>
       </c>
       <c r="R4" t="n">
         <v>2372982000</v>
@@ -1960,161 +1966,155 @@
         <v>23277000</v>
       </c>
       <c r="U4" t="n">
-        <v>19420022000</v>
+        <v>15357621000</v>
       </c>
       <c r="V4" t="n">
-        <v>4982111000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+        <v>3916641000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>2806224000</v>
+        <v>2044914000</v>
       </c>
       <c r="Y4" t="n">
-        <v>467031000</v>
+        <v>428062000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1708856000</v>
+        <v>1443665000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1179119000</v>
+        <v>946947000</v>
       </c>
       <c r="AB4" t="n">
-        <v>529737000</v>
+        <v>496718000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14437911000</v>
+        <v>11440980000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12294715000</v>
+        <v>8877945000</v>
       </c>
       <c r="AE4" t="n">
-        <v>126204000</v>
+        <v>90787000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12168511000</v>
+        <v>8787158000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1350523000</v>
+        <v>1932473000</v>
       </c>
       <c r="AH4" t="n">
-        <v>221425000</v>
+        <v>676684000</v>
       </c>
       <c r="AI4" t="n">
-        <v>766979000</v>
+        <v>679577000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>362119000</v>
+        <v>576212000</v>
       </c>
       <c r="AK4" t="n">
-        <v>28094667000</v>
+        <v>23092922000</v>
       </c>
       <c r="AL4" t="n">
-        <v>8711664000</v>
+        <v>7989372000</v>
       </c>
       <c r="AM4" t="n">
-        <v>62734000</v>
+        <v>29958000</v>
       </c>
       <c r="AN4" t="n">
-        <v>225677000</v>
+        <v>352947000</v>
       </c>
       <c r="AO4" t="n">
-        <v>252685000</v>
+        <v>220704000</v>
       </c>
       <c r="AP4" t="n">
-        <v>102248000</v>
+        <v>97396000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>150437000</v>
+        <v>123308000</v>
       </c>
       <c r="AR4" t="n">
-        <v>394316000</v>
+        <v>358031000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2574563000</v>
+        <v>2330957000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1352547000</v>
+        <v>1187541000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1222016000</v>
+        <v>1143416000</v>
       </c>
       <c r="AV4" t="n">
-        <v>5122080000</v>
+        <v>4607474000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2172453000</v>
+        <v>-2442997000</v>
       </c>
       <c r="AX4" t="n">
-        <v>7294533000</v>
+        <v>7050471000</v>
       </c>
       <c r="AY4" t="n">
-        <v>48363000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5122080000</v>
-      </c>
+        <v>78745000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>1359696000</v>
+        <v>1420195000</v>
       </c>
       <c r="BB4" t="n">
-        <v>5303314000</v>
+        <v>5082511000</v>
       </c>
       <c r="BC4" t="n">
-        <v>583160000</v>
+        <v>469020000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>19383003000</v>
+        <v>15103550000</v>
       </c>
       <c r="BF4" t="n">
-        <v>3249125000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3541551000</v>
-      </c>
+        <v>1371384000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>2782521000</v>
+        <v>3577652000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-33508000</v>
+        <v>-46722000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2472712000</v>
+        <v>3236011000</v>
       </c>
       <c r="BK4" t="n">
-        <v>343317000</v>
+        <v>388363000</v>
       </c>
       <c r="BL4" t="n">
-        <v>7461873000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>106991000</v>
-      </c>
+        <v>8945611000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>376991000</v>
+        <v>764120000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-3644000</v>
+        <v>-16934000</v>
       </c>
       <c r="BP4" t="n">
-        <v>380635000</v>
+        <v>781054000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1703061000</v>
-      </c>
-      <c r="BR4" t="inlineStr"/>
+        <v>324280000</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>134569000</v>
+      </c>
       <c r="BS4" t="n">
-        <v>1703061000</v>
+        <v>189711000</v>
       </c>
       <c r="BT4" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1693061000</v>
+        <v>189711000</v>
       </c>
     </row>
   </sheetData>
@@ -2375,147 +2375,149 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-409622000</v>
+        <v>952042000</v>
       </c>
       <c r="C2" t="n">
-        <v>-5815436000</v>
+        <v>-7861693000</v>
       </c>
       <c r="D2" t="n">
-        <v>5932291000</v>
+        <v>7032969000</v>
       </c>
       <c r="E2" t="n">
-        <v>-584009000</v>
+        <v>-560311000</v>
       </c>
       <c r="F2" t="n">
-        <v>185274000</v>
+        <v>1691133000</v>
       </c>
       <c r="G2" t="n">
-        <v>446110000</v>
+        <v>1939507000</v>
       </c>
       <c r="H2" t="n">
-        <v>26688000</v>
+        <v>-7560000</v>
       </c>
       <c r="I2" t="n">
-        <v>-287524000</v>
+        <v>-240814000</v>
       </c>
       <c r="J2" t="n">
-        <v>-276036000</v>
+        <v>-1535314000</v>
       </c>
       <c r="K2" t="n">
-        <v>35033000</v>
+        <v>-212702000</v>
       </c>
       <c r="L2" t="n">
-        <v>-283581000</v>
+        <v>-316851000</v>
       </c>
       <c r="M2" t="n">
-        <v>116855000</v>
+        <v>-828724000</v>
       </c>
       <c r="N2" t="n">
-        <v>116855000</v>
+        <v>-828724000</v>
       </c>
       <c r="O2" t="n">
-        <v>-5815436000</v>
+        <v>-7861693000</v>
       </c>
       <c r="P2" t="n">
-        <v>5932291000</v>
+        <v>7032969000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-185875000</v>
+        <v>-217853000</v>
       </c>
       <c r="R2" t="n">
-        <v>9324000</v>
+        <v>18056000</v>
       </c>
       <c r="S2" t="n">
-        <v>28831000</v>
+        <v>2817000</v>
       </c>
       <c r="T2" t="n">
-        <v>9050000</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-40950000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>7563000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7563000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>-1785000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-1785000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>1642000</v>
+        <v>-9169000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3209000</v>
+        <v>1061000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1567000</v>
+        <v>-10230000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-242285000</v>
+        <v>-227772000</v>
       </c>
       <c r="AD2" t="n">
-        <v>340157000</v>
+        <v>322309000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-582442000</v>
+        <v>-550081000</v>
       </c>
       <c r="AF2" t="n">
-        <v>174387000</v>
+        <v>1512353000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-104147000</v>
+        <v>-288609000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1278565000</v>
+        <v>-279625000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1246695000</v>
+        <v>259012000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2233331000</v>
+        <v>-364116000</v>
       </c>
       <c r="AK2" t="n">
-        <v>429202000</v>
+        <v>-1330179000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-400322000</v>
+        <v>1118502000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-320809000</v>
+        <v>37156000</v>
       </c>
       <c r="AN2" t="n">
-        <v>544124000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>573486000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>522000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>34272000</v>
+        <v>50303000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>523001000</v>
+        <v>536533000</v>
       </c>
       <c r="AR2" t="n">
-        <v>59722000</v>
+        <v>62046000</v>
       </c>
       <c r="AS2" t="n">
-        <v>463279000</v>
+        <v>474487000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-10524000</v>
+        <v>-963000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-4491000</v>
+        <v>6158000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-8266000</v>
+        <v>-7000</v>
       </c>
       <c r="AW2" t="n">
-        <v>229101000</v>
+        <v>909085000</v>
       </c>
     </row>
     <row r="3">
@@ -2667,149 +2669,147 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>952042000</v>
+        <v>-409622000</v>
       </c>
       <c r="C4" t="n">
-        <v>-7861693000</v>
+        <v>-5815436000</v>
       </c>
       <c r="D4" t="n">
-        <v>7032969000</v>
+        <v>5932291000</v>
       </c>
       <c r="E4" t="n">
-        <v>-560311000</v>
+        <v>-584009000</v>
       </c>
       <c r="F4" t="n">
-        <v>1691133000</v>
+        <v>185274000</v>
       </c>
       <c r="G4" t="n">
-        <v>1939507000</v>
+        <v>446110000</v>
       </c>
       <c r="H4" t="n">
-        <v>-7560000</v>
+        <v>26688000</v>
       </c>
       <c r="I4" t="n">
-        <v>-240814000</v>
+        <v>-287524000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1535314000</v>
+        <v>-276036000</v>
       </c>
       <c r="K4" t="n">
-        <v>-212702000</v>
+        <v>35033000</v>
       </c>
       <c r="L4" t="n">
-        <v>-316851000</v>
+        <v>-283581000</v>
       </c>
       <c r="M4" t="n">
-        <v>-828724000</v>
+        <v>116855000</v>
       </c>
       <c r="N4" t="n">
-        <v>-828724000</v>
+        <v>116855000</v>
       </c>
       <c r="O4" t="n">
-        <v>-7861693000</v>
+        <v>-5815436000</v>
       </c>
       <c r="P4" t="n">
-        <v>7032969000</v>
+        <v>5932291000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-217853000</v>
+        <v>-185875000</v>
       </c>
       <c r="R4" t="n">
-        <v>18056000</v>
+        <v>9324000</v>
       </c>
       <c r="S4" t="n">
-        <v>2817000</v>
+        <v>28831000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>9050000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-40950000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1785000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>-1785000</v>
-      </c>
+        <v>7563000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7563000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-9169000</v>
+        <v>1642000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1061000</v>
+        <v>3209000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-10230000</v>
+        <v>-1567000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-227772000</v>
+        <v>-242285000</v>
       </c>
       <c r="AD4" t="n">
-        <v>322309000</v>
+        <v>340157000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-550081000</v>
+        <v>-582442000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1512353000</v>
+        <v>174387000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-288609000</v>
+        <v>-104147000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-279625000</v>
+        <v>-1278565000</v>
       </c>
       <c r="AI4" t="n">
-        <v>259012000</v>
+        <v>1246695000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-364116000</v>
+        <v>-2233331000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1330179000</v>
+        <v>429202000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1118502000</v>
+        <v>-400322000</v>
       </c>
       <c r="AM4" t="n">
-        <v>37156000</v>
+        <v>-320809000</v>
       </c>
       <c r="AN4" t="n">
-        <v>573486000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>522000</v>
-      </c>
+        <v>544124000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>50303000</v>
+        <v>34272000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>536533000</v>
+        <v>523001000</v>
       </c>
       <c r="AR4" t="n">
-        <v>62046000</v>
+        <v>59722000</v>
       </c>
       <c r="AS4" t="n">
-        <v>474487000</v>
+        <v>463279000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-963000</v>
+        <v>-10524000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6158000</v>
+        <v>-4491000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-7000</v>
+        <v>-8266000</v>
       </c>
       <c r="AW4" t="n">
-        <v>909085000</v>
+        <v>229101000</v>
       </c>
     </row>
   </sheetData>
@@ -3339,192 +3339,192 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Fujiang  Ma', 'age': 60, 'title': 'Executive Chairman of the Board', 'yearBorn': 1965, 'fiscalYear': 2023, 'totalPay': 1158142, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sheng  Wang', 'age': 51, 'title': 'President &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2023, 'totalPay': 12740, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kwan Wai  Leung', 'age': 42, 'title': 'Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Fujiang  Ma', 'age': 60, 'title': 'Executive Chairman of the Board', 'yearBorn': 1965, 'fiscalYear': 2023, 'totalPay': 1157518, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sheng  Wang', 'age': 51, 'title': 'President &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2023, 'totalPay': 12733, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kwan Wai  Leung', 'age': 42, 'title': 'Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.497</v>
+        <v>0.533</v>
       </c>
       <c r="AD2" t="n">
         <v>0.7818182</v>
@@ -3742,10 +3742,10 @@
         <v>2837511429</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1316154</v>
+        <v>3.1299536</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.027461866</v>
+        <v>0.027476447</v>
       </c>
       <c r="BJ2" t="n">
         <v>1703980800</v>
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.1</v>
@@ -3890,141 +3890,141 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>GRAND BAOXIN</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1743408508</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>finmb_143651710</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DF2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DH2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>GRAND BAOXIN</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>-35.820896</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1323826200000</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>Grand Baoxin Auto Group Limited</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.08 - 0.128</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
         <v>0</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DS2" t="n">
         <v>0.0060000047</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DT2" t="n">
         <v>0.07500005999999999</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>0.08 - 0.128</t>
         </is>
       </c>
-      <c r="DM2" t="n">
+      <c r="DV2" t="n">
         <v>-0.042000003</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DW2" t="n">
         <v>-0.328125</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1756205940</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1756814400</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0</v>
       </c>
       <c r="DX2" t="n">
         <v>0</v>
       </c>
       <c r="DY2" t="n">
+        <v>1756205940</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1756814400</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EA2" t="b">
+      <c r="EJ2" t="b">
         <v>0</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1323826200000</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.08 - 0.128</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1743408508</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-35.820896</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.08599999999999999</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
